--- a/artfynd/A 14205-2024 artfynd.xlsx
+++ b/artfynd/A 14205-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120361262</v>
+        <v>120358200</v>
       </c>
       <c r="B2" t="n">
-        <v>91512</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513160</v>
+        <v>513144</v>
       </c>
       <c r="R2" t="n">
-        <v>6761828</v>
+        <v>6761792</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120358200</v>
+        <v>120361262</v>
       </c>
       <c r="B3" t="n">
-        <v>90864</v>
+        <v>91512</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,30 +808,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513144</v>
+        <v>513160</v>
       </c>
       <c r="R3" t="n">
-        <v>6761792</v>
+        <v>6761828</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14205-2024 artfynd.xlsx
+++ b/artfynd/A 14205-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120358200</v>
+        <v>120361262</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>91512</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513144</v>
+        <v>513160</v>
       </c>
       <c r="R2" t="n">
-        <v>6761792</v>
+        <v>6761828</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120361262</v>
+        <v>120358200</v>
       </c>
       <c r="B3" t="n">
-        <v>91512</v>
+        <v>90864</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,30 +808,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513160</v>
+        <v>513144</v>
       </c>
       <c r="R3" t="n">
-        <v>6761828</v>
+        <v>6761792</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14205-2024 artfynd.xlsx
+++ b/artfynd/A 14205-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>120358200</v>
       </c>
       <c r="B2" t="n">
-        <v>90926</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -796,47 +791,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120361262</v>
+        <v>120677966</v>
       </c>
       <c r="B3" t="n">
-        <v>91570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513160</v>
+        <v>513107</v>
       </c>
       <c r="R3" t="n">
-        <v>6761828</v>
+        <v>6761832</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,6 +904,238 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120361262</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>513160</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6761828</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120537885</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>513113</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6761801</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
